--- a/output/pdf_financials_xlsx/BHCC.xlsx
+++ b/output/pdf_financials_xlsx/BHCC.xlsx
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.448509</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.148874</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.017695</v>
+        <v>-0.430814</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.018674</v>
+        <v>-0.1302</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.017695</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.018674</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-10.016369</v>
+        <v>-10.034064</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.315505</v>
+        <v>-0.334179</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-10.016369</v>
+        <v>-10.034064</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.315505</v>
+        <v>-0.334179</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-56605.64566261655</v>
+        <v>-56705.64566261655</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-1689.541608653743</v>
+        <v>-1789.541608653743</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.04308</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.003763</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.00189</v>
       </c>
     </row>
     <row r="35">
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.04308</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.003763</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.00189</v>
       </c>
     </row>
     <row r="37">
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.055877</v>
+        <v>0.012797</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.016535</v>
+        <v>0.012772</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.014625</v>
+        <v>0.012735</v>
       </c>
     </row>
     <row r="49">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" s="5" t="n">
-        <v>-0.448509</v>
+        <v>0.448509</v>
       </c>
       <c r="F79" s="5" t="n">
         <v>-0.148874</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">

--- a/output/pdf_financials_xlsx/BHCC.xlsx
+++ b/output/pdf_financials_xlsx/BHCC.xlsx
@@ -4465,7 +4465,11 @@
           <t>Impairment of private placement</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>0.65</v>
       </c>
